--- a/output/ouvidorias_fais_federais.xlsx
+++ b/output/ouvidorias_fais_federais.xlsx
@@ -424,7 +424,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
@@ -484,22 +484,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FCPC</t>
+          <t>FUNDAPE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fundação Cearense de Pesquisa e Cultura</t>
+          <t>Fundação de Apoio ao Desenvolvimento da Pesquisa e Extensão Universitária no Acre</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UFC</t>
+          <t>UFAC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://fcpc.ufc.br/ouvidoria/</t>
+          <t>https://fundape.com.br/ouvidoria</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -529,29 +529,29 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Ouvidoria própria criada pela Portaria 007/2016; ouvidoria@fcpc.ufc.br.</t>
+          <t>Canal de Ouvidoria próprio + Portal da Transparência (emendas parlamentares).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FINATEC</t>
+          <t>FUNDEPES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fundação de Empreendimentos Científicos e Tecnológicos</t>
+          <t>Fundação Universitária de Desenvolvimento de Extensão e Pesquisa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UnB</t>
+          <t>UFAL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,19 +561,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://www.finatec.org.br</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -581,29 +577,29 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Possui Ouvidoria e Linha Ética; atuação ativa em auditoria e transparência ativa.</t>
+          <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFAL (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FUNAPE</t>
+          <t>UNISOL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa</t>
+          <t>Fundação de Apoio Institucional Rio Solimões</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UFG</t>
+          <t>UFAM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -613,19 +609,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://site.funape.org.br/ouvidoria.php</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -633,29 +625,29 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Página de Ouvidoria própria + Política de Compliance (Lei 13.460/2017).</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFAM (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FUNARBE</t>
+          <t>FAPEX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Universidade Federal de Viçosa</t>
+          <t>Fundação de Apoio à Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UFV</t>
+          <t>UFBA, UFRB, UFOB, UNILAB, IFBA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -675,7 +667,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://funarbe.org.br/a-funarbe/compliance/</t>
+          <t>https://www.fapex.org.br/Fapex/Site/Principal/Home/ouvidoria</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -685,29 +677,29 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Canal de Ouvidoria gerido por escritório externo; ISO 37301/37001; selo CGU 'Pacto Brasil pela Integridade'.</t>
+          <t>Ouvidoria própria (confidencial e imparcial) + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FUNDEP</t>
+          <t>FEPBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fundação de Desenvolvimento da Pesquisa</t>
+          <t>Fundação Escola Politécnica da Bahia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UFMG, UFABC, ITA</t>
+          <t>UFBA, IFBA, UFSB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,19 +709,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://www.fundep.br/canal-de-denuncias/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -737,29 +725,29 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Canal de Denúncias gerido por empresa externa (anonimato); programa de compliance/Código de Conduta.</t>
+          <t>Tem 'Fale Conosco'; sem ouvidoria/canal de denúncias nominal. Transparência via Portal Federal.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FAPEC</t>
+          <t>FCPC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa, ao Ensino e à Cultura</t>
+          <t>Fundação Cearense de Pesquisa e Cultura</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UFMS</t>
+          <t>UFC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -779,7 +767,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://fundacaofapec.org.br</t>
+          <t>https://fcpc.ufc.br/ouvidoria/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -789,29 +777,29 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ouvidoria por e-mail; única fundação credenciada MEC/MCTI de apoio à UFMS.</t>
+          <t>Ouvidoria própria criada pela Portaria 007/2016; ouvidoria@fcpc.ufc.br.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FADESP</t>
+          <t>FAHUB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fundação de Amparo e Desenvolvimento da Pesquisa</t>
+          <t>Fundação de Apoio ao Desenvolvimento Científico e Tecnológico do HUB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UFPA</t>
+          <t>HUB (UnB)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -821,19 +809,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Própria (parcial) + Fala.BR / universidade</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://transparencia.fadesp.org.br/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -841,29 +825,29 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Portal de Transparência próprio; ouvidoria/denúncias direcionadas à Ouvidoria da UFPA (Fala.BR).</t>
+          <t>Ligada ao HUB/UnB (EBSERH); manifestações via Ouvidoria da UnB/HUB (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FADE</t>
+          <t>FINATEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Desenvolvimento da UFPE</t>
+          <t>Fundação de Empreendimentos Científicos e Tecnológicos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UFPE</t>
+          <t>UnB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -883,7 +867,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.fade.org.br</t>
+          <t>https://www.finatec.org.br</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -893,29 +877,29 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Seção de Ouvidoria no portal de transparência; manifestações da sociedade e de pesquisadores.</t>
+          <t>Possui Ouvidoria e Linha Ética; atuação ativa em auditoria e transparência ativa.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPPETEC</t>
+          <t>FEST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fundação Coordenação de Projetos, Pesquisas e Estudos Tecnológicos</t>
+          <t>Fundação Espírito-Santense de Tecnologia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UFES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -935,7 +919,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://ouvidoria.coppetec.coppe.ufrj.br/</t>
+          <t>https://fest.org.br/ouvidoria/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -945,29 +929,29 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (ouvidoria.coppetec.coppe.ufrj.br) + Política de Integridade/Transparência; auditada pelo MP (Curadoria de Fundações).</t>
+          <t>Ouvidoria própria (superintendencia@fest.org.br) + Código de Ética e Normas de Conduta + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FUNPEC</t>
+          <t>FUNAPE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fundação Norte-Rio-Grandense de Pesquisa e Cultura</t>
+          <t>Fundação de Apoio à Pesquisa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UFRN</t>
+          <t>UFG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -987,7 +971,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.funpec.br</t>
+          <t>https://site.funape.org.br/ouvidoria.php</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -997,29 +981,29 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Disponibiliza canal de Ouvidoria e Serviço de Informação ao Cidadão (SIC).</t>
+          <t>Página de Ouvidoria própria + Política de Compliance (Lei 13.460/2017).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FAI.UFSCAR</t>
+          <t>FUNDAHC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fundação de Apoio Institucional ao Desenvolvimento Científico e Tecnológico</t>
+          <t>Fundação de Apoio ao Hospital das Clínicas da UFG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UFSCar</t>
+          <t>UFG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1029,17 +1013,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Própria (parcial) + Fala.BR / universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.fai.ufscar.br/transparencia/home/index/1</t>
+          <t>https://fundahc.org.br/p/487-ouvidoria</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1049,29 +1033,29 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Tem Portal da Transparência próprio, mas NÃO possui ouvidoria/canal de denúncias nominal. Ouvidoria via UFSCar (ouvidoria.ufscar.br) e CPE-UFSCar / Fala.BR.</t>
+          <t>Ouvidoria própria com plataforma SieOuv (Lei 13.460), Canal de Denúncias e SIC; ouvidoria@fundahc.com.br.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FAP UNIFESP</t>
+          <t>RTVE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à UNIFESP</t>
+          <t>Fundação RTVE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIFESP, UFABC</t>
+          <t>UFG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1091,7 +1075,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.fapunifesp.edu.br</t>
+          <t>https://rtve.org.br/ouvidoria/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1101,29 +1085,29 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Canal de comunicação direta para transparência/compliance; LGPD e Portal da Transparência.</t>
+          <t>Ouvidoria própria (ouvidoria@rtve.org.br, 10 dias úteis) + Canal de Denúncias/Compliance + Transparência.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FUNDAPE</t>
+          <t>FJM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Desenvolvimento da Pesquisa e Extensão</t>
+          <t>Fundação Josué Montello</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UFAC</t>
+          <t>UFMA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1133,41 +1117,45 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Apoia o HU-UFMA; busca não localizou canal próprio. Manifestações via UFMA/Fala.BR.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FUNDEPES</t>
+          <t>FSADU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fundação Universitária de Desenvolvimento de Extensão e Pesquisa</t>
+          <t>Fundação Sousândrade de Apoio ao Desenvolvimento da UFMA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UFAL</t>
+          <t>UFMA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1177,41 +1165,49 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://fsadu.org.br/sugestoes-e-criticas/</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Canal de denúncias/sugestões/críticas próprio (anonimato + antirretaliação).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UNISOL</t>
+          <t>FACEPE-UNIFAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fundação Universidade Solidária</t>
+          <t>Fundação de Apoio à Cultura, Ensino, Pesquisa e Extensão de Alfenas</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UFAM</t>
+          <t>UNIFAL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1221,41 +1217,45 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UNIFAL-MG (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>FACEV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fundação Escola de Administração</t>
+          <t>Fundação Artística, Cultural e de Educação para a Cidadania de Viçosa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UFBA</t>
+          <t>UFV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1265,41 +1265,49 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.facev.org/ouvidoria</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Canal de Denúncias próprio (Lei 14.457/22, sigilo, antirretaliação) + Código de Conduta.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FAPEX</t>
+          <t>FADEPE/JF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa e Extensão</t>
+          <t>Fundação de Apoio e Desenvolvimento ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UFBA, UFRB, UFOB, UNILAB, IFBA</t>
+          <t>UFJF</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1309,41 +1317,45 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Tem 'Fale Conosco'; sem ouvidoria nominal. Manifestações via Ouvidoria da UFJF (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FEPBA</t>
+          <t>FAEPE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fundação Escola Politécnica da Bahia</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UFBA, IFBA, UFSB</t>
+          <t>UFLA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1353,41 +1365,45 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Canal de contato (Fale Conosco) para reclamações/denúncias; sem ouvidoria nominal. Via UFLA/Fala.BR.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASTEF</t>
+          <t>FAEPU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fundação Cearense de Apoio ao Desenvolvimento Científico e Tecnológico</t>
+          <t>Fundação de Assistência, Estudo e Pesquisa de Uberlândia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UFC</t>
+          <t>UFU</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1397,41 +1413,49 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://www.faepu.org.br/pagina/canal-denuncias-faepu</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Canal de Denúncias próprio (confidencial).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FAHUB</t>
+          <t>FAPEPE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Hospital Universitário de Brasília</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão de Itajubá</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HUB (UnB)</t>
+          <t>UNIFEI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1441,41 +1465,49 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://fapepe.conveniar.com.br/portaltransparencia/</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Portal de Transparência próprio + Fale Conosco; ouvidoria via UNIFEI (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FEST</t>
+          <t>FAU-UFU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fundação Espírito-Santense de Tecnologia</t>
+          <t>Fundação de Apoio Universitário</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UFES</t>
+          <t>UFU</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1485,41 +1517,49 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://fau.org.br/etica-e-compliance/</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Programa de Integridade + Canal de Denúncias seguro e confidencial.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FAUF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fundação Ceciliano Abel de Almeida</t>
+          <t>Fundação de Apoio à Universidade Federal de São João del-Rei</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UFES</t>
+          <t>UFSJ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1529,41 +1569,45 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFSJ (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FUNDAHC</t>
+          <t>FCO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Hospital das Clínicas da UFG</t>
+          <t>Fundação Christiano Ottoni</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UFG</t>
+          <t>UFMG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1573,41 +1617,49 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://fco.org.br</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Comitê de Ética e Transparência + Código de Integridade e Transparência; ouvidoria/canal de denúncias nominal não localizado.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RTVE</t>
+          <t>FCT/JF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fundação RTVE</t>
+          <t>Fundação para Pesquisa Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UFG</t>
+          <t>UFJF</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1617,41 +1669,45 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFJF (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FJM</t>
+          <t>FEOP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fundação Josué Montello</t>
+          <t>Fundação Educativa de Rádio e TV Ouro Preto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UFMA</t>
+          <t>UFOP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1661,41 +1717,45 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Fundação educativa de rádio/TV da UFOP; sem canal próprio. Manifestações via Ouvidoria da UFOP (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FSADU</t>
+          <t>FEPE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fundação Sousândrade de Apoio ao Desenvolvimento da UFMA</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UFMA</t>
+          <t>UFMG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1705,36 +1765,44 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.fepe.com.br/contatos/</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Canal de Ouvidoria/Denúncias próprio (ouvidoria@fepe.com.br, anônimo).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FACEPE-UNIFAL</t>
+          <t>FHU</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Cultura, Ensino, Pesquisa e Extensão</t>
+          <t>Fundação do Hospital Universitário da UFJF</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UNIFAL</t>
+          <t>UFJF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1749,31 +1817,35 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Ligada ao HU-UFJF (EBSERH); manifestações via Ouvidoria do HU-UFJF / UFJF (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FACEV</t>
+          <t>FUNARBE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fundação de Apoio e Desenvolvimento Científico</t>
+          <t>Fundação de Apoio à Universidade Federal de Viçosa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1793,36 +1865,44 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://funarbe.org.br/a-funarbe/compliance/</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Canal de Ouvidoria gerido por escritório externo; ISO 37301/37001; selo CGU 'Pacto Brasil pela Integridade'.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FADEPE/JF</t>
+          <t>FUNDAEPE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fundação de Apoio e Desenvolvimento ao Ensino, Pesquisa e Extensão</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UFJF</t>
+          <t>UFVJM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1837,31 +1917,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFVJM (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FAEPE</t>
+          <t>FUNDECC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
+          <t>Fundação de Desenvolvimento Científico e Cultural</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1881,36 +1965,44 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.fundecc.org.br/denuncias/</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Canal próprio de denúncias (/denuncias/). UFLA também mantém ouvidoria autônoma.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FAEPU</t>
+          <t>FUNDEP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fundação de Assistência, Estudo e Pesquisa de Uberlândia</t>
+          <t>Fundação de Desenvolvimento da Pesquisa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UFU</t>
+          <t>UFMG, UFABC, ITA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1925,31 +2017,39 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.fundep.br/canal-de-denuncias/</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Canal de Denúncias gerido por empresa externa (anonimato); programa de compliance/Código de Conduta.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FAPEPE</t>
+          <t>FUPAI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa, Ensino e Extensão</t>
+          <t>Fundação de Pesquisa e Assessoramento à Indústria</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1969,36 +2069,40 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Busca não localizou canal próprio de ouvidoria; manifestações via UNIFEI/Fala.BR.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FAU-UFU</t>
+          <t>GORCEIX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fundação de Apoio Universitário</t>
+          <t>Fundação Gorceix</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UFU</t>
+          <t>UFOP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2013,36 +2117,44 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://site.gorceix.org.br/transparencia</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Portal da Transparência próprio; manifestações de ouvidoria via UFOP (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FAUF</t>
+          <t>IMEPEN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Universidade Federal de São João del-Rei</t>
+          <t>Fundação IMEPEN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UFSJ</t>
+          <t>UFJF</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2057,31 +2169,35 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFJF (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FCO</t>
+          <t>IPEAD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fundação Christiano Ottoni</t>
+          <t>Fundação Instituto de Pesquisas Econômicas, Administrativas e Contábeis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2101,41 +2217,49 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://site.ipead.face.ufmg.br/contato/</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Ouvidoria própria (0800 000 7110, WhatsApp, ipead@ipead.face.ufmg.br) + Portal da Transparência.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FCT/JF</t>
+          <t>FAPEC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fundação para Pesquisa Científica e Tecnológica</t>
+          <t>Fundação de Apoio à Pesquisa, ao Ensino e à Cultura</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UFJF</t>
+          <t>UFMS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2145,41 +2269,49 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://fundacaofapec.org.br</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Ouvidoria por e-mail; única fundação credenciada MEC/MCTI de apoio à UFMS.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FEOP</t>
+          <t>FUNAEPE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fundação Educativa de Ouro Preto</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UFOP</t>
+          <t>UFGD</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2189,41 +2321,45 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFGD (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FEPE</t>
+          <t>UNISELVA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fundação de Ensino e Pesquisa</t>
+          <t>Fundação de Apoio e Desenvolvimento da UFMT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UFMG</t>
+          <t>UFMT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2233,41 +2369,49 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://webunisig.fundacaouniselva.org.br/transparencia/</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Portal da Transparência próprio; ouvidoria via UFMT (ouvidoria@ufmt.br / Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FHU</t>
+          <t>FADESP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fundação do Hospital Universitário da UFJF</t>
+          <t>Fundação de Amparo e Desenvolvimento da Pesquisa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UFJF</t>
+          <t>UFPA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2277,26 +2421,34 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://transparencia.fadesp.org.br/</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Portal de Transparência próprio; ouvidoria/denúncias direcionadas à Ouvidoria da UFPA (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FUNDAEPE</t>
+          <t>FUNPEA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2306,12 +2458,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UFVJM</t>
+          <t>UFPA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2321,41 +2473,45 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPA (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FUNDECC</t>
+          <t>PaqTcPB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fundação de Desenvolvimento Científico e Cultural</t>
+          <t>Fundação Parque Tecnológico da Paraíba</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UFLA</t>
+          <t>UFCG</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2365,41 +2521,45 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Busca não localizou canal próprio de ouvidoria; manifestações via UFCG/Fala.BR.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FUPAI</t>
+          <t>FADE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fundação de Pesquisa e Assessoramento à Indústria</t>
+          <t>Fundação de Apoio ao Desenvolvimento da UFPE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UNIFEI</t>
+          <t>UFPE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2409,41 +2569,49 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.fade.org.br</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Seção de Ouvidoria no portal de transparência; manifestações da sociedade e de pesquisadores.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GORCEIX</t>
+          <t>FADURPE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fundação Gorceix</t>
+          <t>Fundação Apolônio Salles de Desenvolvimento Educacional</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UFOP</t>
+          <t>UFRPE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2453,41 +2621,45 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRPE (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IMEPEN</t>
+          <t>FADEX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fundação IMEPEN</t>
+          <t>Fundação Cultural e de Fomento à Pesquisa, Ensino, Extensão e Inovação</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UFJF</t>
+          <t>UFPI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2497,41 +2669,49 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.fadex.org.br/dados_contatos</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Ouvidoria própria (ouvidoria@fadex.org.br, monitorada pela superintendência).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IPEAD</t>
+          <t>FUNPAR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fundação Instituto de Pesquisas Econômicas, Administrativas e Contábeis</t>
+          <t>Fundação da Universidade Federal do Paraná</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UFMG</t>
+          <t>UFPR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2541,41 +2721,49 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.funpar.ufpr.br/paginas.php?page=39</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Ouvidoria própria (canal de reclamações, sugestões, denúncias e elogios) + Portal da Transparência.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FUNAEPE</t>
+          <t>FUNTEF-PR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
+          <t>Fundação de Apoio à Educação, Pesquisa e Desenvolvimento Científico</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UFGD</t>
+          <t>UTFPR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2585,41 +2773,49 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://funtefpr.org.br/fale-conosco/</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Ouvidoria/Fale Conosco (formulário + superintendencia@funtefpr.org.br) + Portal da Transparência.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UNISELVA</t>
+          <t>FUPEF</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fundação de Apoio e Desenvolvimento da UFMT</t>
+          <t>Fundação de Pesquisas Florestais do Paraná</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UFMT</t>
+          <t>UFPR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2629,41 +2825,49 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://fupef.org.br/ouvidoria/</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Página de Ouvidoria própria + Portal da Transparência.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FUNPEA</t>
+          <t>BIORIO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
+          <t>Fundação Bio-Rio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UFPA</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2673,41 +2877,45 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRJ (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PaqTcPB</t>
+          <t>COPPETEC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fundação Parque Tecnológico da Paraíba</t>
+          <t>Fundação Coordenação de Projetos, Pesquisas e Estudos Tecnológicos</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UFCG</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2717,41 +2925,49 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://ouvidoria.coppetec.coppe.ufrj.br/</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Ouvidoria própria (ouvidoria.coppetec.coppe.ufrj.br) + Política de Integridade/Transparência; auditada pelo MP (Curadoria de Fundações).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FADURPE</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fundação Apolônio Salles de Desenvolvimento Educacional</t>
+          <t>Fundação Euclides da Cunha</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UFRPE</t>
+          <t>UFF</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2761,41 +2977,49 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://somosfec.org.br/compliance-denuncias/</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Canal de Ética/Denúncias próprio (confidencial, anônimo, antirretaliação) + Compliance + Transparência.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FADEX</t>
+          <t>FUJB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fundação Cultural e de Fomento à Pesquisa, Ensino e Extensão</t>
+          <t>Fundação Universitária José Bonifácio</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UFPI</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2805,41 +3029,49 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.fujb.ufrj.br</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Site traz seções de Ouvidoria e Transparência próprias.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FUNPAR</t>
+          <t>FURJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fundação da Universidade Federal do Paraná</t>
+          <t>Fundação Universitária José Bonifácio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UFPR</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2849,41 +3081,45 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRJ (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FUNTEF-PR</t>
+          <t>FGD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Educação, Pesquisa e Desenvolvimento Científico</t>
+          <t>Fundação Guimarães Duque</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UTFPR</t>
+          <t>UFERSA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2893,41 +3129,45 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFERSA (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FUPEF</t>
+          <t>FUNPEC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fundação de Pesquisas Florestais do Paraná</t>
+          <t>Fundação Norte-Rio-Grandense de Pesquisa e Cultura</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UFPR</t>
+          <t>UFRN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2937,41 +3177,49 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.funpec.br</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Disponibiliza canal de Ouvidoria e Serviço de Informação ao Cidadão (SIC).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BIORIO</t>
+          <t>FAHERG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fundação Bio-Rio</t>
+          <t>Fundação de Apoio ao Hospital de Ensino do Rio Grande</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>HU-FURG</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2981,41 +3229,45 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Ligada ao HU-FURG (EBSERH); manifestações via Ouvidoria do HU-FURG (ouv.hu-furg@ebserh.gov.br / Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FATEC-UFSM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fundação Euclides da Cunha</t>
+          <t>Fundação de Apoio à Tecnologia e Ciência</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UFF</t>
+          <t>UFSM</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3025,41 +3277,45 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Tem controles internos, mas sem ouvidoria pública identificada; manifestações via UFSM/Fala.BR.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FUJB</t>
+          <t>FAURG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fundação Universidade-Empresa de Tecnologia e Ciências (José Bonifácio)</t>
+          <t>Fundação de Apoio à Universidade Federal do Rio Grande</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>FURG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3069,41 +3325,45 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da FURG (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FUNRIO</t>
+          <t>FAURGS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa e Extensão</t>
+          <t>Fundação de Apoio da Universidade Federal do Rio Grande do Sul</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UFRGS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3113,41 +3373,45 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFRGS (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FURJ</t>
+          <t>FDMS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fundação Universitária José Bonifácio</t>
+          <t>Fundação Delfim Mendes Silveira</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UFPel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3157,41 +3421,45 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPel (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FGD</t>
+          <t>FEEng</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fundação Guimarães Duque</t>
+          <t>Fundação Empresa Escola de Engenharia da UFRGS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UFERSA</t>
+          <t>UFRGS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3201,36 +3469,44 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.ufrgs.br/feeng/?page_id=81</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Ouvidoria própria (ouvidoria@feeng.com.br).</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FAHERG</t>
+          <t>FLE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Hospital Universitário (Dr. Riet Corrêa Jr.)</t>
+          <t>Fundação Luiz Englert</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HU-FURG</t>
+          <t>UFRGS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3245,36 +3521,40 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Canais de contato, sem ouvidoria nominal; manifestações via Ouvidoria da UFRGS (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FATEC-UFSM</t>
+          <t>FSB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Tecnologia e Ciência</t>
+          <t>Fundação Simon Bolívar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UFSM</t>
+          <t>UFPel</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3289,36 +3569,40 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPel (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FAURG</t>
+          <t>FUNDMED</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Universidade Federal do Rio Grande</t>
+          <t>Fundação Médica do Rio Grande do Sul</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FURG</t>
+          <t>UFRGS / HCPA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3333,41 +3617,49 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://fundmed.org.br/en/compliance-program/</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Canal de Ética e Conduta gerido por empresa externa (Ouvidor Digital) + Programa de Compliance e Política Anticorrupção.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FAURGS</t>
+          <t>FAPEU</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fundação de Apoio da Universidade Federal do Rio Grande do Sul</t>
+          <t>Fundação de Amparo à Pesquisa e Extensão Universitária</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>UFSC, IFSC, UFFS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3377,41 +3669,49 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.contatoseguro.com.br/fapeu</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Canal de Denúncias próprio via Contato Seguro (0800 900 9099, anônimo) + Portal da Transparência.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FDMS</t>
+          <t>FEESC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fundação Delfim Mendes Silveira</t>
+          <t>Fundação de Ensino e Engenharia de Santa Catarina (Stemmer)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UFPel</t>
+          <t>UFSC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3421,41 +3721,49 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.feesc.org.br</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Portal de Transparência próprio + referência a Canal de Denúncias; ouvidoria nominal a confirmar.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FEEng</t>
+          <t>FEPESE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fundação Empresa Escola de Engenharia da UFRGS</t>
+          <t>Fundação de Estudos e Pesquisas Socioeconômicos</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>UFSC</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3465,41 +3773,45 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Canais de contato (reclamações/sugestões), sem ouvidoria nominal identificada; via UFSC/Fala.BR.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FLE</t>
+          <t>FUNJAB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fundação Luiz Englert</t>
+          <t>Fundação José Arthur Boiteux</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>UFSC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3509,41 +3821,45 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Tem normas/compliance, mas manifestações são direcionadas à Ouvidoria da UFSC.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FSB</t>
+          <t>FAPESE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fundação Simon Bolívar</t>
+          <t>Fundação de Apoio à Pesquisa e Extensão de Sergipe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UFPel</t>
+          <t>UFS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3553,41 +3869,45 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFS (Fala.BR).</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FUNDMED</t>
+          <t>FAI.UFSCAR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fundação Médica do Rio Grande do Sul</t>
+          <t>Fundação de Apoio Institucional ao Desenvolvimento Científico e Tecnológico</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UFRGS / HCPA</t>
+          <t>UFSCar</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3597,41 +3917,49 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.fai.ufscar.br/transparencia/home/index/1</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Tem Portal da Transparência próprio, mas NÃO possui ouvidoria/canal de denúncias nominal. Ouvidoria via UFSCar (ouvidoria.ufscar.br) e CPE-UFSCar / Fala.BR.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FAPEU</t>
+          <t>FAP UNIFESP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fundação de Amparo à Pesquisa e Extensão Universitária</t>
+          <t>Fundação de Apoio à UNIFESP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UFSC, IFSC, UFFS</t>
+          <t>UNIFESP, UFABC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3641,41 +3969,49 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.fapunifesp.edu.br</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Canal de comunicação direta para transparência/compliance; LGPD e Portal da Transparência.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FEESC</t>
+          <t>FAPTO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fundação de Ensino e Engenharia de Santa Catarina (Stemmer)</t>
+          <t>Fundação de Apoio Científico e Tecnológico do Tocantins</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UFSC</t>
+          <t>UFT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3685,41 +4021,49 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://fapto.org.br</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Menciona canal de denúncias confidencial + Portal de Transparência (com falhas apontadas pela CGU). Ouvidoria nominal a confirmar.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FEPESE</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fundação de Estudos e Pesquisas Socioeconômicos</t>
+          <t>Fundação Escola de Administração</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UFSC</t>
+          <t>UFBA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3743,27 +4087,31 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Vínculo a esclarecer: a UFBA afirma que a Fundação Escola de Administração da Bahia (FEA-BA) NÃO é sua fundação de apoio.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FUNJAB</t>
+          <t>ASTEF</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fundação José Arthur Boiteux</t>
+          <t>Fundação ASTEF / FASTEF (Apoio a Serviços Técnicos, Ensino e Fomento a Pesquisas)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UFSC</t>
+          <t>UFC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3787,27 +4135,31 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>A ASTEF instituiu a FASTEF (fundação de apoio à UFC); tem Acesso à Informação institucional; canal de ouvidoria próprio a confirmar.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FAPESE</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa e Extensão de Sergipe</t>
+          <t>Fundação de Apoio Cassiano Antônio Moraes</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UFS</t>
+          <t>UFES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3831,27 +4183,31 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Ligada ao HUCAM/UFES. (A antiga Fundação Ceciliano Abel de Almeida está em liquidação judicial.) Canal próprio a confirmar.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FAPTO</t>
+          <t>FUNRIO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fundação de Apoio Científico e Tecnológico do Tocantins</t>
+          <t>Fundação de Apoio à Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UFT</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3875,7 +4231,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Busca inicial não localizou site/canal próprio com confiança (homônimo com organizadora de concursos); reconfirmar.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3924,7 +4284,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -3934,7 +4294,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3944,7 +4304,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -3954,7 +4314,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3964,7 +4324,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/output/ouvidorias_fais_federais.xlsx
+++ b/output/ouvidorias_fais_federais.xlsx
@@ -632,17 +632,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FAPEX</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa e Extensão</t>
+          <t>Fundação ADM (Escola de Administração)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UFBA, UFRB, UFOB, UNILAB, IFBA</t>
+          <t>UFBA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -657,19 +657,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://www.fapex.org.br/Fapex/Site/Principal/Home/ouvidoria</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -677,24 +673,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (confidencial e imparcial) + Portal da Transparência.</t>
+          <t>Ligada à Escola de Administração da UFBA; sem canal próprio identificado. Obs.: a UFBA não a lista entre suas fundações de apoio credenciadas (FEPBA e FAPEX); vínculo formal a confirmar.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FEPBA</t>
+          <t>FAPEX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fundação Escola Politécnica da Bahia</t>
+          <t>Fundação de Apoio à Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UFBA, IFBA, UFSB</t>
+          <t>UFBA, UFRB, UFOB, UNILAB, IFBA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -709,15 +705,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.fapex.org.br/Fapex/Site/Principal/Home/ouvidoria</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -725,29 +725,29 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Tem 'Fale Conosco'; sem ouvidoria/canal de denúncias nominal. Transparência via Portal Federal.</t>
+          <t>Ouvidoria própria (confidencial e imparcial) + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCPC</t>
+          <t>FEPBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fundação Cearense de Pesquisa e Cultura</t>
+          <t>Fundação Escola Politécnica da Bahia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UFC</t>
+          <t>UFBA, IFBA, UFSB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -757,19 +757,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://fcpc.ufc.br/ouvidoria/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -777,29 +773,29 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ouvidoria própria criada pela Portaria 007/2016; ouvidoria@fcpc.ufc.br.</t>
+          <t>Tem 'Fale Conosco'; sem ouvidoria/canal de denúncias nominal. Transparência via Portal Federal.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FAHUB</t>
+          <t>ASTEF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Desenvolvimento Científico e Tecnológico do HUB</t>
+          <t>Fundação ASTEF / FASTEF (Apoio a Serviços Técnicos, Ensino e Fomento a Pesquisas)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HUB (UnB)</t>
+          <t>UFC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -809,15 +805,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://fastef.ufc.br/informacao-institucional/</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -825,29 +825,29 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ligada ao HUB/UnB (EBSERH); manifestações via Ouvidoria da UnB/HUB (Fala.BR).</t>
+          <t>A ASTEF instituiu a FASTEF (fundação de apoio à UFC). Tem Acesso à Informação institucional; canal de ouvidoria/denúncias nominal não localizado; via UFC/Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FINATEC</t>
+          <t>FCPC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fundação de Empreendimentos Científicos e Tecnológicos</t>
+          <t>Fundação Cearense de Pesquisa e Cultura</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UnB</t>
+          <t>UFC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.finatec.org.br</t>
+          <t>https://fcpc.ufc.br/ouvidoria/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -877,29 +877,29 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Possui Ouvidoria e Linha Ética; atuação ativa em auditoria e transparência ativa.</t>
+          <t>Ouvidoria própria criada pela Portaria 007/2016; ouvidoria@fcpc.ufc.br.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FEST</t>
+          <t>FAHUB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fundação Espírito-Santense de Tecnologia</t>
+          <t>Fundação de Apoio ao Desenvolvimento Científico e Tecnológico do HUB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UFES</t>
+          <t>HUB (UnB)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,19 +909,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://fest.org.br/ouvidoria/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -929,29 +925,29 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (superintendencia@fest.org.br) + Código de Ética e Normas de Conduta + Portal da Transparência.</t>
+          <t>Ligada ao HUB/UnB (EBSERH); manifestações via Ouvidoria da UnB/HUB (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FUNAPE</t>
+          <t>FINATEC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa</t>
+          <t>Fundação de Empreendimentos Científicos e Tecnológicos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UFG</t>
+          <t>UnB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -971,7 +967,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://site.funape.org.br/ouvidoria.php</t>
+          <t>https://www.finatec.org.br</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -981,29 +977,29 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Página de Ouvidoria própria + Política de Compliance (Lei 13.460/2017).</t>
+          <t>Possui Ouvidoria e Linha Ética; atuação ativa em auditoria e transparência ativa.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FUNDAHC</t>
+          <t>FEST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Hospital das Clínicas da UFG</t>
+          <t>Fundação Espírito-Santense de Tecnologia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UFG</t>
+          <t>UFES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1023,7 +1019,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://fundahc.org.br/p/487-ouvidoria</t>
+          <t>https://fest.org.br/ouvidoria/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1033,29 +1029,29 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Ouvidoria própria com plataforma SieOuv (Lei 13.460), Canal de Denúncias e SIC; ouvidoria@fundahc.com.br.</t>
+          <t>Ouvidoria própria (superintendencia@fest.org.br) + Código de Ética e Normas de Conduta + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RTVE</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fundação RTVE</t>
+          <t>Fundação de Apoio Cassiano Antônio Moraes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UFG</t>
+          <t>UFES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1065,19 +1061,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://rtve.org.br/ouvidoria/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1085,29 +1077,29 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (ouvidoria@rtve.org.br, 10 dias úteis) + Canal de Denúncias/Compliance + Transparência.</t>
+          <t>Ligada ao HUCAM/UFES (EBSERH); sem canal próprio identificado, manifestações via HUCAM/UFES (Fala.BR). (A antiga Fundação Ceciliano Abel de Almeida está em liquidação judicial.)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FJM</t>
+          <t>FUNAPE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fundação Josué Montello</t>
+          <t>Fundação de Apoio à Pesquisa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UFMA</t>
+          <t>UFG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1117,15 +1109,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://site.funape.org.br/ouvidoria.php</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1133,29 +1129,29 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Apoia o HU-UFMA; busca não localizou canal próprio. Manifestações via UFMA/Fala.BR.</t>
+          <t>Página de Ouvidoria própria + Política de Compliance (Lei 13.460/2017).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FSADU</t>
+          <t>FUNDAHC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fundação Sousândrade de Apoio ao Desenvolvimento da UFMA</t>
+          <t>Fundação de Apoio ao Hospital das Clínicas da UFG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UFMA</t>
+          <t>UFG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1175,7 +1171,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://fsadu.org.br/sugestoes-e-criticas/</t>
+          <t>https://fundahc.org.br/p/487-ouvidoria</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1185,29 +1181,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Canal de denúncias/sugestões/críticas próprio (anonimato + antirretaliação).</t>
+          <t>Ouvidoria própria com plataforma SieOuv (Lei 13.460), Canal de Denúncias e SIC; ouvidoria@fundahc.com.br.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FACEPE-UNIFAL</t>
+          <t>RTVE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Cultura, Ensino, Pesquisa e Extensão de Alfenas</t>
+          <t>Fundação RTVE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNIFAL</t>
+          <t>UFG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1217,15 +1213,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://rtve.org.br/ouvidoria/</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UNIFAL-MG (Fala.BR).</t>
+          <t>Ouvidoria própria (ouvidoria@rtve.org.br, 10 dias úteis) + Canal de Denúncias/Compliance + Transparência.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FACEV</t>
+          <t>FJM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fundação Artística, Cultural e de Educação para a Cidadania de Viçosa</t>
+          <t>Fundação Josué Montello</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UFV</t>
+          <t>UFMA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1265,19 +1265,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.facev.org/ouvidoria</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1285,29 +1281,29 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Canal de Denúncias próprio (Lei 14.457/22, sigilo, antirretaliação) + Código de Conduta.</t>
+          <t>Apoia o HU-UFMA; busca não localizou canal próprio. Manifestações via UFMA/Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FADEPE/JF</t>
+          <t>FSADU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fundação de Apoio e Desenvolvimento ao Ensino, Pesquisa e Extensão</t>
+          <t>Fundação Sousândrade de Apoio ao Desenvolvimento da UFMA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UFJF</t>
+          <t>UFMA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1317,15 +1313,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://fsadu.org.br/sugestoes-e-criticas/</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Tem 'Fale Conosco'; sem ouvidoria nominal. Manifestações via Ouvidoria da UFJF (Fala.BR).</t>
+          <t>Canal de denúncias/sugestões/críticas próprio (anonimato + antirretaliação).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FAEPE</t>
+          <t>FACEPE-UNIFAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
+          <t>Fundação de Apoio à Cultura, Ensino, Pesquisa e Extensão de Alfenas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UFLA</t>
+          <t>UNIFAL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1381,24 +1381,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Canal de contato (Fale Conosco) para reclamações/denúncias; sem ouvidoria nominal. Via UFLA/Fala.BR.</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UNIFAL-MG (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FAEPU</t>
+          <t>FACEV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fundação de Assistência, Estudo e Pesquisa de Uberlândia</t>
+          <t>Fundação Artística, Cultural e de Educação para a Cidadania de Viçosa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UFU</t>
+          <t>UFV</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://www.faepu.org.br/pagina/canal-denuncias-faepu</t>
+          <t>https://www.facev.org/ouvidoria</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Canal de Denúncias próprio (confidencial).</t>
+          <t>Canal de Denúncias próprio (Lei 14.457/22, sigilo, antirretaliação) + Código de Conduta.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FAPEPE</t>
+          <t>FADEPE/JF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão de Itajubá</t>
+          <t>Fundação de Apoio e Desenvolvimento ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UNIFEI</t>
+          <t>UFJF</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1465,19 +1465,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Própria (parcial) + Fala.BR / universidade</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>http://fapepe.conveniar.com.br/portaltransparencia/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1485,24 +1481,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Portal de Transparência próprio + Fale Conosco; ouvidoria via UNIFEI (Fala.BR).</t>
+          <t>Tem 'Fale Conosco'; sem ouvidoria nominal. Manifestações via Ouvidoria da UFJF (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FAU-UFU</t>
+          <t>FAEPE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fundação de Apoio Universitário</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UFU</t>
+          <t>UFLA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1517,19 +1513,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://fau.org.br/etica-e-compliance/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1537,24 +1529,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Programa de Integridade + Canal de Denúncias seguro e confidencial.</t>
+          <t>Canal de contato (Fale Conosco) para reclamações/denúncias; sem ouvidoria nominal. Via UFLA/Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FAUF</t>
+          <t>FAEPU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Universidade Federal de São João del-Rei</t>
+          <t>Fundação de Assistência, Estudo e Pesquisa de Uberlândia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UFSJ</t>
+          <t>UFU</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1569,15 +1561,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>http://www.faepu.org.br/pagina/canal-denuncias-faepu</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1585,24 +1581,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFSJ (Fala.BR).</t>
+          <t>Canal de Denúncias próprio (confidencial).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FCO</t>
+          <t>FAPEPE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fundação Christiano Ottoni</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão de Itajubá</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UFMG</t>
+          <t>UNIFEI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1627,7 +1623,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://fco.org.br</t>
+          <t>http://fapepe.conveniar.com.br/portaltransparencia/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1637,24 +1633,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Comitê de Ética e Transparência + Código de Integridade e Transparência; ouvidoria/canal de denúncias nominal não localizado.</t>
+          <t>Portal de Transparência próprio + Fale Conosco; ouvidoria via UNIFEI (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FCT/JF</t>
+          <t>FAU-UFU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fundação para Pesquisa Científica e Tecnológica</t>
+          <t>Fundação de Apoio Universitário</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UFJF</t>
+          <t>UFU</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1669,15 +1665,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://fau.org.br/etica-e-compliance/</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1685,24 +1685,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFJF (Fala.BR).</t>
+          <t>Programa de Integridade + Canal de Denúncias seguro e confidencial.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FEOP</t>
+          <t>FAUF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fundação Educativa de Rádio e TV Ouro Preto</t>
+          <t>Fundação de Apoio à Universidade Federal de São João del-Rei</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UFOP</t>
+          <t>UFSJ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1733,19 +1733,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Fundação educativa de rádio/TV da UFOP; sem canal próprio. Manifestações via Ouvidoria da UFOP (Fala.BR).</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFSJ (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FEPE</t>
+          <t>FCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
+          <t>Fundação Christiano Ottoni</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.fepe.com.br/contatos/</t>
+          <t>https://fco.org.br</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1785,19 +1785,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Canal de Ouvidoria/Denúncias próprio (ouvidoria@fepe.com.br, anônimo).</t>
+          <t>Comitê de Ética e Transparência + Código de Integridade e Transparência; ouvidoria/canal de denúncias nominal não localizado.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FHU</t>
+          <t>FCT/JF</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fundação do Hospital Universitário da UFJF</t>
+          <t>Fundação para Pesquisa Científica e Tecnológica</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1833,24 +1833,24 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ligada ao HU-UFJF (EBSERH); manifestações via Ouvidoria do HU-UFJF / UFJF (Fala.BR).</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFJF (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FUNARBE</t>
+          <t>FEOP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Universidade Federal de Viçosa</t>
+          <t>Fundação Educativa de Rádio e TV Ouro Preto</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UFV</t>
+          <t>UFOP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1865,19 +1865,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://funarbe.org.br/a-funarbe/compliance/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1885,14 +1881,14 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Canal de Ouvidoria gerido por escritório externo; ISO 37301/37001; selo CGU 'Pacto Brasil pela Integridade'.</t>
+          <t>Fundação educativa de rádio/TV da UFOP; sem canal próprio. Manifestações via Ouvidoria da UFOP (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FUNDAEPE</t>
+          <t>FEPE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1902,7 +1898,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UFVJM</t>
+          <t>UFMG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1917,15 +1913,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.fepe.com.br/contatos/</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1933,24 +1933,24 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFVJM (Fala.BR).</t>
+          <t>Canal de Ouvidoria/Denúncias próprio (ouvidoria@fepe.com.br, anônimo).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FUNDECC</t>
+          <t>FHU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fundação de Desenvolvimento Científico e Cultural</t>
+          <t>Fundação do Hospital Universitário da UFJF</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UFLA</t>
+          <t>UFJF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1965,19 +1965,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://www.fundecc.org.br/denuncias/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -1985,24 +1981,24 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Canal próprio de denúncias (/denuncias/). UFLA também mantém ouvidoria autônoma.</t>
+          <t>Ligada ao HU-UFJF (EBSERH); manifestações via Ouvidoria do HU-UFJF / UFJF (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FUNDEP</t>
+          <t>FUNARBE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fundação de Desenvolvimento da Pesquisa</t>
+          <t>Fundação de Apoio à Universidade Federal de Viçosa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UFMG, UFABC, ITA</t>
+          <t>UFV</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2027,7 +2023,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.fundep.br/canal-de-denuncias/</t>
+          <t>https://funarbe.org.br/a-funarbe/compliance/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2037,24 +2033,24 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Canal de Denúncias gerido por empresa externa (anonimato); programa de compliance/Código de Conduta.</t>
+          <t>Canal de Ouvidoria gerido por escritório externo; ISO 37301/37001; selo CGU 'Pacto Brasil pela Integridade'.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FUPAI</t>
+          <t>FUNDAEPE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fundação de Pesquisa e Assessoramento à Indústria</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UNIFEI</t>
+          <t>UFVJM</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2085,24 +2081,24 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Busca não localizou canal próprio de ouvidoria; manifestações via UNIFEI/Fala.BR.</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFVJM (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GORCEIX</t>
+          <t>FUNDECC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fundação Gorceix</t>
+          <t>Fundação de Desenvolvimento Científico e Cultural</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UFOP</t>
+          <t>UFLA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2117,17 +2113,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Própria (parcial) + Fala.BR / universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://site.gorceix.org.br/transparencia</t>
+          <t>https://www.fundecc.org.br/denuncias/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2137,24 +2133,24 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Portal da Transparência próprio; manifestações de ouvidoria via UFOP (Fala.BR).</t>
+          <t>Canal próprio de denúncias (/denuncias/). UFLA também mantém ouvidoria autônoma.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IMEPEN</t>
+          <t>FUNDEP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fundação IMEPEN</t>
+          <t>Fundação de Desenvolvimento da Pesquisa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UFJF</t>
+          <t>UFMG, UFABC, ITA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2169,15 +2165,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.fundep.br/canal-de-denuncias/</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -2185,24 +2185,24 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFJF (Fala.BR).</t>
+          <t>Canal de Denúncias gerido por empresa externa (anonimato); programa de compliance/Código de Conduta.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IPEAD</t>
+          <t>FUPAI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fundação Instituto de Pesquisas Econômicas, Administrativas e Contábeis</t>
+          <t>Fundação de Pesquisa e Assessoramento à Indústria</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UFMG</t>
+          <t>UNIFEI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2217,19 +2217,15 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://site.ipead.face.ufmg.br/contato/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -2237,29 +2233,29 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (0800 000 7110, WhatsApp, ipead@ipead.face.ufmg.br) + Portal da Transparência.</t>
+          <t>Busca não localizou canal próprio de ouvidoria; manifestações via UNIFEI/Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FAPEC</t>
+          <t>GORCEIX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa, ao Ensino e à Cultura</t>
+          <t>Fundação Gorceix</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UFMS</t>
+          <t>UFOP</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2269,17 +2265,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://fundacaofapec.org.br</t>
+          <t>https://site.gorceix.org.br/transparencia</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2289,29 +2285,29 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Ouvidoria por e-mail; única fundação credenciada MEC/MCTI de apoio à UFMS.</t>
+          <t>Portal da Transparência próprio; manifestações de ouvidoria via UFOP (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FUNAEPE</t>
+          <t>IMEPEN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
+          <t>Fundação IMEPEN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UFGD</t>
+          <t>UFJF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2337,29 +2333,29 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFGD (Fala.BR).</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFJF (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UNISELVA</t>
+          <t>IPEAD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fundação de Apoio e Desenvolvimento da UFMT</t>
+          <t>Fundação Instituto de Pesquisas Econômicas, Administrativas e Contábeis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UFMT</t>
+          <t>UFMG</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2369,17 +2365,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Própria (parcial) + Fala.BR / universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://webunisig.fundacaouniselva.org.br/transparencia/</t>
+          <t>https://site.ipead.face.ufmg.br/contato/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2389,29 +2385,29 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Portal da Transparência próprio; ouvidoria via UFMT (ouvidoria@ufmt.br / Fala.BR).</t>
+          <t>Ouvidoria própria (0800 000 7110, WhatsApp, ipead@ipead.face.ufmg.br) + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FADESP</t>
+          <t>FAPEC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fundação de Amparo e Desenvolvimento da Pesquisa</t>
+          <t>Fundação de Apoio à Pesquisa, ao Ensino e à Cultura</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UFPA</t>
+          <t>UFMS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2421,17 +2417,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Própria (parcial) + Fala.BR / universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://transparencia.fadesp.org.br/</t>
+          <t>https://fundacaofapec.org.br</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2441,14 +2437,14 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Portal de Transparência próprio; ouvidoria/denúncias direcionadas à Ouvidoria da UFPA (Fala.BR).</t>
+          <t>Ouvidoria por e-mail; única fundação credenciada MEC/MCTI de apoio à UFMS.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FUNPEA</t>
+          <t>FUNAEPE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2458,12 +2454,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UFPA</t>
+          <t>UFGD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2489,29 +2485,29 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPA (Fala.BR).</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFGD (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PaqTcPB</t>
+          <t>UNISELVA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fundação Parque Tecnológico da Paraíba</t>
+          <t>Fundação de Apoio e Desenvolvimento da UFMT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UFCG</t>
+          <t>UFMT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2521,15 +2517,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://webunisig.fundacaouniselva.org.br/transparencia/</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -2537,29 +2537,29 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Busca não localizou canal próprio de ouvidoria; manifestações via UFCG/Fala.BR.</t>
+          <t>Portal da Transparência próprio; ouvidoria via UFMT (ouvidoria@ufmt.br / Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FADE</t>
+          <t>FADESP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Desenvolvimento da UFPE</t>
+          <t>Fundação de Amparo e Desenvolvimento da Pesquisa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UFPE</t>
+          <t>UFPA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.fade.org.br</t>
+          <t>https://transparencia.fadesp.org.br/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2589,29 +2589,29 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Seção de Ouvidoria no portal de transparência; manifestações da sociedade e de pesquisadores.</t>
+          <t>Portal de Transparência próprio; ouvidoria/denúncias direcionadas à Ouvidoria da UFPA (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FADURPE</t>
+          <t>FUNPEA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fundação Apolônio Salles de Desenvolvimento Educacional</t>
+          <t>Fundação de Apoio ao Ensino, Pesquisa e Extensão</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UFRPE</t>
+          <t>UFPA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2637,29 +2637,29 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRPE (Fala.BR).</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPA (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FADEX</t>
+          <t>PaqTcPB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fundação Cultural e de Fomento à Pesquisa, Ensino, Extensão e Inovação</t>
+          <t>Fundação Parque Tecnológico da Paraíba</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UFPI</t>
+          <t>UFCG</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2669,19 +2669,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>https://www.fadex.org.br/dados_contatos</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -2689,29 +2685,29 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (ouvidoria@fadex.org.br, monitorada pela superintendência).</t>
+          <t>Busca não localizou canal próprio de ouvidoria; manifestações via UFCG/Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FUNPAR</t>
+          <t>FADE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fundação da Universidade Federal do Paraná</t>
+          <t>Fundação de Apoio ao Desenvolvimento da UFPE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UFPR</t>
+          <t>UFPE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2731,7 +2727,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.funpar.ufpr.br/paginas.php?page=39</t>
+          <t>https://www.fade.org.br</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2741,29 +2737,29 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (canal de reclamações, sugestões, denúncias e elogios) + Portal da Transparência.</t>
+          <t>Seção de Ouvidoria no portal de transparência; manifestações da sociedade e de pesquisadores.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FUNTEF-PR</t>
+          <t>FADURPE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Educação, Pesquisa e Desenvolvimento Científico</t>
+          <t>Fundação Apolônio Salles de Desenvolvimento Educacional</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UTFPR</t>
+          <t>UFRPE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2773,19 +2769,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://funtefpr.org.br/fale-conosco/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -2793,29 +2785,29 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Ouvidoria/Fale Conosco (formulário + superintendencia@funtefpr.org.br) + Portal da Transparência.</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRPE (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FUPEF</t>
+          <t>FADEX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fundação de Pesquisas Florestais do Paraná</t>
+          <t>Fundação Cultural e de Fomento à Pesquisa, Ensino, Extensão e Inovação</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UFPR</t>
+          <t>UFPI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2835,7 +2827,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://fupef.org.br/ouvidoria/</t>
+          <t>https://www.fadex.org.br/dados_contatos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2845,29 +2837,29 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Página de Ouvidoria própria + Portal da Transparência.</t>
+          <t>Ouvidoria própria (ouvidoria@fadex.org.br, monitorada pela superintendência).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BIORIO</t>
+          <t>FUNPAR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fundação Bio-Rio</t>
+          <t>Fundação da Universidade Federal do Paraná</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UFPR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2877,15 +2869,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.funpar.ufpr.br/paginas.php?page=39</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -2893,29 +2889,29 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRJ (Fala.BR).</t>
+          <t>Ouvidoria própria (canal de reclamações, sugestões, denúncias e elogios) + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COPPETEC</t>
+          <t>FUNTEF-PR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fundação Coordenação de Projetos, Pesquisas e Estudos Tecnológicos</t>
+          <t>Fundação de Apoio à Educação, Pesquisa e Desenvolvimento Científico</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UTFPR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2935,7 +2931,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://ouvidoria.coppetec.coppe.ufrj.br/</t>
+          <t>https://funtefpr.org.br/fale-conosco/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2945,29 +2941,29 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (ouvidoria.coppetec.coppe.ufrj.br) + Política de Integridade/Transparência; auditada pelo MP (Curadoria de Fundações).</t>
+          <t>Ouvidoria/Fale Conosco (formulário + superintendencia@funtefpr.org.br) + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FUPEF</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fundação Euclides da Cunha</t>
+          <t>Fundação de Pesquisas Florestais do Paraná</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UFF</t>
+          <t>UFPR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2987,7 +2983,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://somosfec.org.br/compliance-denuncias/</t>
+          <t>https://fupef.org.br/ouvidoria/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2997,19 +2993,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Canal de Ética/Denúncias próprio (confidencial, anônimo, antirretaliação) + Compliance + Transparência.</t>
+          <t>Página de Ouvidoria própria + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FUJB</t>
+          <t>BIORIO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fundação Universitária José Bonifácio</t>
+          <t>Fundação Bio-Rio</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3029,19 +3025,15 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>https://www.fujb.ufrj.br</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3049,19 +3041,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Site traz seções de Ouvidoria e Transparência próprias.</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRJ (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FURJ</t>
+          <t>COPPETEC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fundação Universitária José Bonifácio</t>
+          <t>Fundação Coordenação de Projetos, Pesquisas e Estudos Tecnológicos</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3081,15 +3073,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://ouvidoria.coppetec.coppe.ufrj.br/</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3097,29 +3093,29 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRJ (Fala.BR).</t>
+          <t>Ouvidoria própria (ouvidoria.coppetec.coppe.ufrj.br) + Política de Integridade/Transparência; auditada pelo MP (Curadoria de Fundações).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FGD</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fundação Guimarães Duque</t>
+          <t>Fundação Euclides da Cunha</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UFERSA</t>
+          <t>UFF</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3129,15 +3125,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://somosfec.org.br/compliance-denuncias/</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3145,29 +3145,29 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFERSA (Fala.BR).</t>
+          <t>Canal de Ética/Denúncias próprio (confidencial, anônimo, antirretaliação) + Compliance + Transparência.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FUNPEC</t>
+          <t>FUJB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fundação Norte-Rio-Grandense de Pesquisa e Cultura</t>
+          <t>Fundação Universitária José Bonifácio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UFRN</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.funpec.br</t>
+          <t>https://www.fujb.ufrj.br</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3197,29 +3197,29 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Disponibiliza canal de Ouvidoria e Serviço de Informação ao Cidadão (SIC).</t>
+          <t>Site traz seções de Ouvidoria e Transparência próprias.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FAHERG</t>
+          <t>FUNRIO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fundação de Apoio ao Hospital de Ensino do Rio Grande</t>
+          <t>Fundação de Apoio à Pesquisa, Ensino e Assistência (Gaffrée e Guinle)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HU-FURG</t>
+          <t>UNIRIO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3245,29 +3245,29 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Ligada ao HU-FURG (EBSERH); manifestações via Ouvidoria do HU-FURG (ouv.hu-furg@ebserh.gov.br / Fala.BR).</t>
+          <t>Vínculo corrigido: apoia a UNIRIO e o HU Gaffrée e Guinle (não a UFRJ). Sem canal próprio identificado; via UNIRIO/Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FATEC-UFSM</t>
+          <t>FURJ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Tecnologia e Ciência</t>
+          <t>Fundação Universitária José Bonifácio</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UFSM</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3293,29 +3293,29 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Tem controles internos, mas sem ouvidoria pública identificada; manifestações via UFSM/Fala.BR.</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRJ (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FAURG</t>
+          <t>FGD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Universidade Federal do Rio Grande</t>
+          <t>Fundação Guimarães Duque</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FURG</t>
+          <t>UFERSA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3341,29 +3341,29 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da FURG (Fala.BR).</t>
+          <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFERSA (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FAURGS</t>
+          <t>FUNPEC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fundação de Apoio da Universidade Federal do Rio Grande do Sul</t>
+          <t>Fundação Norte-Rio-Grandense de Pesquisa e Cultura</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>UFRN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3373,15 +3373,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.funpec.br</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3389,24 +3393,24 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFRGS (Fala.BR).</t>
+          <t>Disponibiliza canal de Ouvidoria e Serviço de Informação ao Cidadão (SIC).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FDMS</t>
+          <t>FAHERG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fundação Delfim Mendes Silveira</t>
+          <t>Fundação de Apoio ao Hospital de Ensino do Rio Grande</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UFPel</t>
+          <t>HU-FURG</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3437,24 +3441,24 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPel (Fala.BR).</t>
+          <t>Ligada ao HU-FURG (EBSERH); manifestações via Ouvidoria do HU-FURG (ouv.hu-furg@ebserh.gov.br / Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FEEng</t>
+          <t>FATEC-UFSM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fundação Empresa Escola de Engenharia da UFRGS</t>
+          <t>Fundação de Apoio à Tecnologia e Ciência</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>UFSM</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3469,19 +3473,15 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>https://www.ufrgs.br/feeng/?page_id=81</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3489,24 +3489,24 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Ouvidoria própria (ouvidoria@feeng.com.br).</t>
+          <t>Tem controles internos, mas sem ouvidoria pública identificada; manifestações via UFSM/Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FLE</t>
+          <t>FAURG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fundação Luiz Englert</t>
+          <t>Fundação de Apoio à Universidade Federal do Rio Grande</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>FURG</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3537,24 +3537,24 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Canais de contato, sem ouvidoria nominal; manifestações via Ouvidoria da UFRGS (Fala.BR).</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da FURG (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FSB</t>
+          <t>FAURGS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fundação Simon Bolívar</t>
+          <t>Fundação de Apoio da Universidade Federal do Rio Grande do Sul</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UFPel</t>
+          <t>UFRGS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3585,24 +3585,24 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPel (Fala.BR).</t>
+          <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFRGS (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FUNDMED</t>
+          <t>FDMS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fundação Médica do Rio Grande do Sul</t>
+          <t>Fundação Delfim Mendes Silveira</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UFRGS / HCPA</t>
+          <t>UFPel</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3617,19 +3617,15 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>https://fundmed.org.br/en/compliance-program/</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3637,29 +3633,29 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Canal de Ética e Conduta gerido por empresa externa (Ouvidor Digital) + Programa de Compliance e Política Anticorrupção.</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPel (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FAPEU</t>
+          <t>FEEng</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fundação de Amparo à Pesquisa e Extensão Universitária</t>
+          <t>Fundação Empresa Escola de Engenharia da UFRGS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UFSC, IFSC, UFFS</t>
+          <t>UFRGS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3679,7 +3675,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.contatoseguro.com.br/fapeu</t>
+          <t>https://www.ufrgs.br/feeng/?page_id=81</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3689,29 +3685,29 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Canal de Denúncias próprio via Contato Seguro (0800 900 9099, anônimo) + Portal da Transparência.</t>
+          <t>Ouvidoria própria (ouvidoria@feeng.com.br).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FEESC</t>
+          <t>FLE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fundação de Ensino e Engenharia de Santa Catarina (Stemmer)</t>
+          <t>Fundação Luiz Englert</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UFSC</t>
+          <t>UFRGS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3721,19 +3717,15 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Própria (parcial) + Fala.BR / universidade</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>https://www.feesc.org.br</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3741,29 +3733,29 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Portal de Transparência próprio + referência a Canal de Denúncias; ouvidoria nominal a confirmar.</t>
+          <t>Canais de contato, sem ouvidoria nominal; manifestações via Ouvidoria da UFRGS (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FEPESE</t>
+          <t>FSB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fundação de Estudos e Pesquisas Socioeconômicos</t>
+          <t>Fundação Simon Bolívar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UFSC</t>
+          <t>UFPel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3789,29 +3781,29 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Canais de contato (reclamações/sugestões), sem ouvidoria nominal identificada; via UFSC/Fala.BR.</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPel (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FUNJAB</t>
+          <t>FUNDMED</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fundação José Arthur Boiteux</t>
+          <t>Fundação Médica do Rio Grande do Sul</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UFSC</t>
+          <t>UFRGS / HCPA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3821,15 +3813,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://fundmed.org.br/en/compliance-program/</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3837,29 +3833,29 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Tem normas/compliance, mas manifestações são direcionadas à Ouvidoria da UFSC.</t>
+          <t>Canal de Ética e Conduta gerido por empresa externa (Ouvidor Digital) + Programa de Compliance e Política Anticorrupção.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FAPESE</t>
+          <t>FAPEU</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa e Extensão de Sergipe</t>
+          <t>Fundação de Amparo à Pesquisa e Extensão Universitária</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UFS</t>
+          <t>UFSC, IFSC, UFFS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3869,15 +3865,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fala.BR / ouvidoria da universidade</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.contatoseguro.com.br/fapeu</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3885,29 +3885,29 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFS (Fala.BR).</t>
+          <t>Canal de Denúncias próprio via Contato Seguro (0800 900 9099, anônimo) + Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FAI.UFSCAR</t>
+          <t>FEESC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fundação de Apoio Institucional ao Desenvolvimento Científico e Tecnológico</t>
+          <t>Fundação de Ensino e Engenharia de Santa Catarina (Stemmer)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UFSCar</t>
+          <t>UFSC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.fai.ufscar.br/transparencia/home/index/1</t>
+          <t>https://www.feesc.org.br</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3937,29 +3937,29 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Tem Portal da Transparência próprio, mas NÃO possui ouvidoria/canal de denúncias nominal. Ouvidoria via UFSCar (ouvidoria.ufscar.br) e CPE-UFSCar / Fala.BR.</t>
+          <t>Portal de Transparência próprio + referência a Canal de Denúncias; ouvidoria nominal a confirmar.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FAP UNIFESP</t>
+          <t>FEPESE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à UNIFESP</t>
+          <t>Fundação de Estudos e Pesquisas Socioeconômicos</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UNIFESP, UFABC</t>
+          <t>UFSC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3969,19 +3969,15 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Própria</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>https://www.fapunifesp.edu.br</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -3989,29 +3985,29 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Canal de comunicação direta para transparência/compliance; LGPD e Portal da Transparência.</t>
+          <t>Canais de contato (reclamações/sugestões), sem ouvidoria nominal identificada; via UFSC/Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FAPTO</t>
+          <t>FUNJAB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fundação de Apoio Científico e Tecnológico do Tocantins</t>
+          <t>Fundação José Arthur Boiteux</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UFT</t>
+          <t>UFSC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4021,19 +4017,15 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Própria (parcial) + Fala.BR / universidade</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>https://fapto.org.br</t>
-        </is>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Verificado</t>
@@ -4041,29 +4033,29 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Menciona canal de denúncias confidencial + Portal de Transparência (com falhas apontadas pela CGU). Ouvidoria nominal a confirmar.</t>
+          <t>Tem normas/compliance, mas manifestações são direcionadas à Ouvidoria da UFSC.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>FAPESE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fundação Escola de Administração</t>
+          <t>Fundação de Apoio à Pesquisa e Extensão de Sergipe</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UFBA</t>
+          <t>UFS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4073,45 +4065,45 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Fala.BR / ouvidoria da universidade</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Vínculo a esclarecer: a UFBA afirma que a Fundação Escola de Administração da Bahia (FEA-BA) NÃO é sua fundação de apoio.</t>
+          <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFS (Fala.BR).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ASTEF</t>
+          <t>FAI.UFSCAR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fundação ASTEF / FASTEF (Apoio a Serviços Técnicos, Ensino e Fomento a Pesquisas)</t>
+          <t>Fundação de Apoio Institucional ao Desenvolvimento Científico e Tecnológico</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UFC</t>
+          <t>UFSCar</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4121,45 +4113,49 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.fai.ufscar.br/transparencia/home/index/1</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>A ASTEF instituiu a FASTEF (fundação de apoio à UFC); tem Acesso à Informação institucional; canal de ouvidoria próprio a confirmar.</t>
+          <t>Tem Portal da Transparência próprio, mas NÃO possui ouvidoria/canal de denúncias nominal. Ouvidoria via UFSCar (ouvidoria.ufscar.br) e CPE-UFSCar / Fala.BR.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FAP UNIFESP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fundação de Apoio Cassiano Antônio Moraes</t>
+          <t>Fundação de Apoio à UNIFESP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UFES</t>
+          <t>UNIFESP, UFABC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4169,45 +4165,49 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.fapunifesp.edu.br</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Ligada ao HUCAM/UFES. (A antiga Fundação Ceciliano Abel de Almeida está em liquidação judicial.) Canal próprio a confirmar.</t>
+          <t>Canal de comunicação direta para transparência/compliance; LGPD e Portal da Transparência.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FUNRIO</t>
+          <t>FAPTO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fundação de Apoio à Pesquisa e Extensão</t>
+          <t>Fundação de Apoio Científico e Tecnológico do Tocantins</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UFT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4217,23 +4217,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Própria (parcial) + Fala.BR / universidade</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>A verificar</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://fapto.org.br</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Busca inicial não localizou site/canal próprio com confiança (homônimo com organizadora de concursos); reconfirmar.</t>
+          <t>Menciona canal de denúncias confidencial + Portal de Transparência (com falhas apontadas pela CGU). Ouvidoria nominal a confirmar.</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4298,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -4304,7 +4308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -4314,7 +4318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4324,7 +4328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/output/ouvidorias_fais_federais.xlsx
+++ b/output/ouvidorias_fais_federais.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -424,9 +424,10 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,15 +468,20 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Canal / URL</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Verificação</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
@@ -519,15 +525,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>https://fundape.com.br/ouvidoria</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Canal de Ouvidoria próprio + Portal da Transparência (emendas parlamentares).</t>
         </is>
@@ -569,13 +580,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFAL (Fala.BR).</t>
         </is>
@@ -617,13 +633,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFAM (Fala.BR).</t>
         </is>
@@ -665,13 +686,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Ligada à Escola de Administração da UFBA; sem canal próprio identificado. Obs.: a UFBA não a lista entre suas fundações de apoio credenciadas (FEPBA e FAPEX); vínculo formal a confirmar.</t>
         </is>
@@ -715,15 +741,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>https://www.fapex.org.br/Fapex/Site/Principal/Home/ouvidoria</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Ouvidoria própria (confidencial e imparcial) + Portal da Transparência.</t>
         </is>
@@ -765,13 +796,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Tem 'Fale Conosco'; sem ouvidoria/canal de denúncias nominal. Transparência via Portal Federal.</t>
         </is>
@@ -815,15 +851,20 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>https://fastef.ufc.br/informacao-institucional/</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>A ASTEF instituiu a FASTEF (fundação de apoio à UFC). Tem Acesso à Informação institucional; canal de ouvidoria/denúncias nominal não localizado; via UFC/Fala.BR.</t>
         </is>
@@ -867,15 +908,20 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>https://fcpc.ufc.br/ouvidoria/</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Ouvidoria própria criada pela Portaria 007/2016; ouvidoria@fcpc.ufc.br.</t>
         </is>
@@ -917,13 +963,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Ligada ao HUB/UnB (EBSERH); manifestações via Ouvidoria da UnB/HUB (Fala.BR).</t>
         </is>
@@ -967,15 +1018,20 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>https://www.finatec.org.br</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Possui Ouvidoria e Linha Ética; atuação ativa em auditoria e transparência ativa.</t>
         </is>
@@ -1019,15 +1075,20 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>https://fest.org.br/ouvidoria/</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Ouvidoria própria (superintendencia@fest.org.br) + Código de Ética e Normas de Conduta + Portal da Transparência.</t>
         </is>
@@ -1069,13 +1130,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Ligada ao HUCAM/UFES (EBSERH); sem canal próprio identificado, manifestações via HUCAM/UFES (Fala.BR). (A antiga Fundação Ceciliano Abel de Almeida está em liquidação judicial.)</t>
         </is>
@@ -1119,15 +1185,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>https://site.funape.org.br/ouvidoria.php</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Página de Ouvidoria própria + Política de Compliance (Lei 13.460/2017).</t>
         </is>
@@ -1171,15 +1242,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>https://fundahc.org.br/p/487-ouvidoria</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Ouvidoria própria com plataforma SieOuv (Lei 13.460), Canal de Denúncias e SIC; ouvidoria@fundahc.com.br.</t>
         </is>
@@ -1223,15 +1299,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>https://rtve.org.br/ouvidoria/</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Ouvidoria própria (ouvidoria@rtve.org.br, 10 dias úteis) + Canal de Denúncias/Compliance + Transparência.</t>
         </is>
@@ -1273,13 +1354,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Apoia o HU-UFMA; busca não localizou canal próprio. Manifestações via UFMA/Fala.BR.</t>
         </is>
@@ -1323,15 +1409,20 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>https://fsadu.org.br/sugestoes-e-criticas/</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Canal de denúncias/sugestões/críticas próprio (anonimato + antirretaliação).</t>
         </is>
@@ -1373,13 +1464,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UNIFAL-MG (Fala.BR).</t>
         </is>
@@ -1423,15 +1519,20 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>https://www.facev.org/ouvidoria</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Canal de Denúncias próprio (Lei 14.457/22, sigilo, antirretaliação) + Código de Conduta.</t>
         </is>
@@ -1473,13 +1574,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Tem 'Fale Conosco'; sem ouvidoria nominal. Manifestações via Ouvidoria da UFJF (Fala.BR).</t>
         </is>
@@ -1521,13 +1627,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Canal de contato (Fale Conosco) para reclamações/denúncias; sem ouvidoria nominal. Via UFLA/Fala.BR.</t>
         </is>
@@ -1571,15 +1682,20 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>http://www.faepu.org.br/pagina/canal-denuncias-faepu</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Canal de Denúncias próprio (confidencial).</t>
         </is>
@@ -1623,15 +1739,20 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>http://fapepe.conveniar.com.br/portaltransparencia/</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Portal de Transparência próprio + Fale Conosco; ouvidoria via UNIFEI (Fala.BR).</t>
         </is>
@@ -1675,15 +1796,20 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>https://fau.org.br/etica-e-compliance/</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Programa de Integridade + Canal de Denúncias seguro e confidencial.</t>
         </is>
@@ -1725,13 +1851,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFSJ (Fala.BR).</t>
         </is>
@@ -1775,15 +1906,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>https://fco.org.br</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Comitê de Ética e Transparência + Código de Integridade e Transparência; ouvidoria/canal de denúncias nominal não localizado.</t>
         </is>
@@ -1825,13 +1961,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFJF (Fala.BR).</t>
         </is>
@@ -1873,13 +2014,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Fundação educativa de rádio/TV da UFOP; sem canal próprio. Manifestações via Ouvidoria da UFOP (Fala.BR).</t>
         </is>
@@ -1923,15 +2069,20 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>https://www.fepe.com.br/contatos/</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Canal de Ouvidoria/Denúncias próprio (ouvidoria@fepe.com.br, anônimo).</t>
         </is>
@@ -1973,13 +2124,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Ligada ao HU-UFJF (EBSERH); manifestações via Ouvidoria do HU-UFJF / UFJF (Fala.BR).</t>
         </is>
@@ -2023,15 +2179,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>https://funarbe.org.br/a-funarbe/compliance/</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Canal de Ouvidoria gerido por escritório externo; ISO 37301/37001; selo CGU 'Pacto Brasil pela Integridade'.</t>
         </is>
@@ -2073,13 +2234,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFVJM (Fala.BR).</t>
         </is>
@@ -2123,15 +2289,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>https://www.fundecc.org.br/denuncias/</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Canal próprio de denúncias (/denuncias/). UFLA também mantém ouvidoria autônoma.</t>
         </is>
@@ -2175,15 +2346,20 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>https://www.fundep.br/canal-de-denuncias/</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Canal de Denúncias gerido por empresa externa (anonimato); programa de compliance/Código de Conduta.</t>
         </is>
@@ -2225,13 +2401,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Busca não localizou canal próprio de ouvidoria; manifestações via UNIFEI/Fala.BR.</t>
         </is>
@@ -2275,15 +2456,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>https://site.gorceix.org.br/transparencia</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Portal da Transparência próprio; manifestações de ouvidoria via UFOP (Fala.BR).</t>
         </is>
@@ -2325,13 +2511,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFJF (Fala.BR).</t>
         </is>
@@ -2375,15 +2566,20 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>https://site.ipead.face.ufmg.br/contato/</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Ouvidoria própria (0800 000 7110, WhatsApp, ipead@ipead.face.ufmg.br) + Portal da Transparência.</t>
         </is>
@@ -2427,15 +2623,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>https://fundacaofapec.org.br</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Ouvidoria por e-mail; única fundação credenciada MEC/MCTI de apoio à UFMS.</t>
         </is>
@@ -2477,13 +2678,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFGD (Fala.BR).</t>
         </is>
@@ -2527,15 +2733,20 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>https://webunisig.fundacaouniselva.org.br/transparencia/</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Portal da Transparência próprio; ouvidoria via UFMT (ouvidoria@ufmt.br / Fala.BR).</t>
         </is>
@@ -2579,15 +2790,20 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>https://transparencia.fadesp.org.br/</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Portal de Transparência próprio; ouvidoria/denúncias direcionadas à Ouvidoria da UFPA (Fala.BR).</t>
         </is>
@@ -2629,13 +2845,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPA (Fala.BR).</t>
         </is>
@@ -2677,13 +2898,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Busca não localizou canal próprio de ouvidoria; manifestações via UFCG/Fala.BR.</t>
         </is>
@@ -2727,15 +2953,20 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>https://www.fade.org.br</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Seção de Ouvidoria no portal de transparência; manifestações da sociedade e de pesquisadores.</t>
         </is>
@@ -2777,13 +3008,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRPE (Fala.BR).</t>
         </is>
@@ -2827,15 +3063,20 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>https://www.fadex.org.br/dados_contatos</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Ouvidoria própria (ouvidoria@fadex.org.br, monitorada pela superintendência).</t>
         </is>
@@ -2879,15 +3120,20 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>https://www.funpar.ufpr.br/paginas.php?page=39</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Ouvidoria própria (canal de reclamações, sugestões, denúncias e elogios) + Portal da Transparência.</t>
         </is>
@@ -2931,15 +3177,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>https://funtefpr.org.br/fale-conosco/</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Ouvidoria/Fale Conosco (formulário + superintendencia@funtefpr.org.br) + Portal da Transparência.</t>
         </is>
@@ -2983,15 +3234,20 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
           <t>https://fupef.org.br/ouvidoria/</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Página de Ouvidoria própria + Portal da Transparência.</t>
         </is>
@@ -3033,13 +3289,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRJ (Fala.BR).</t>
         </is>
@@ -3083,15 +3344,20 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>https://ouvidoria.coppetec.coppe.ufrj.br/</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Ouvidoria própria (ouvidoria.coppetec.coppe.ufrj.br) + Política de Integridade/Transparência; auditada pelo MP (Curadoria de Fundações).</t>
         </is>
@@ -3135,15 +3401,20 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>https://somosfec.org.br/compliance-denuncias/</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Canal de Ética/Denúncias próprio (confidencial, anônimo, antirretaliação) + Compliance + Transparência.</t>
         </is>
@@ -3187,15 +3458,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>https://www.fujb.ufrj.br</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Site traz seções de Ouvidoria e Transparência próprias.</t>
         </is>
@@ -3237,13 +3513,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>Vínculo corrigido: apoia a UNIRIO e o HU Gaffrée e Guinle (não a UFRJ). Sem canal próprio identificado; via UNIRIO/Fala.BR.</t>
         </is>
@@ -3285,13 +3566,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFRJ (Fala.BR).</t>
         </is>
@@ -3333,13 +3619,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFERSA (Fala.BR).</t>
         </is>
@@ -3383,15 +3674,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>https://www.funpec.br</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Disponibiliza canal de Ouvidoria e Serviço de Informação ao Cidadão (SIC).</t>
         </is>
@@ -3433,13 +3729,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Ligada ao HU-FURG (EBSERH); manifestações via Ouvidoria do HU-FURG (ouv.hu-furg@ebserh.gov.br / Fala.BR).</t>
         </is>
@@ -3481,13 +3782,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>Tem controles internos, mas sem ouvidoria pública identificada; manifestações via UFSM/Fala.BR.</t>
         </is>
@@ -3529,13 +3835,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da FURG (Fala.BR).</t>
         </is>
@@ -3577,13 +3888,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Busca não localizou canal próprio; manifestações via Ouvidoria da UFRGS (Fala.BR).</t>
         </is>
@@ -3625,13 +3941,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPel (Fala.BR).</t>
         </is>
@@ -3675,15 +3996,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>https://www.ufrgs.br/feeng/?page_id=81</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Ouvidoria própria (ouvidoria@feeng.com.br).</t>
         </is>
@@ -3725,13 +4051,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Canais de contato, sem ouvidoria nominal; manifestações via Ouvidoria da UFRGS (Fala.BR).</t>
         </is>
@@ -3773,13 +4104,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFPel (Fala.BR).</t>
         </is>
@@ -3823,15 +4159,20 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>https://fundmed.org.br/en/compliance-program/</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Canal de Ética e Conduta gerido por empresa externa (Ouvidor Digital) + Programa de Compliance e Política Anticorrupção.</t>
         </is>
@@ -3875,15 +4216,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
           <t>https://www.contatoseguro.com.br/fapeu</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>Canal de Denúncias próprio via Contato Seguro (0800 900 9099, anônimo) + Portal da Transparência.</t>
         </is>
@@ -3927,15 +4273,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
           <t>https://www.feesc.org.br</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Portal de Transparência próprio + referência a Canal de Denúncias; ouvidoria nominal a confirmar.</t>
         </is>
@@ -3977,13 +4328,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>Canais de contato (reclamações/sugestões), sem ouvidoria nominal identificada; via UFSC/Fala.BR.</t>
         </is>
@@ -4025,13 +4381,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>Tem normas/compliance, mas manifestações são direcionadas à Ouvidoria da UFSC.</t>
         </is>
@@ -4073,13 +4434,18 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>Sem canal próprio identificado; manifestações via Ouvidoria da UFS (Fala.BR).</t>
         </is>
@@ -4123,15 +4489,20 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>https://www.fai.ufscar.br/transparencia/home/index/1</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>Tem Portal da Transparência próprio, mas NÃO possui ouvidoria/canal de denúncias nominal. Ouvidoria via UFSCar (ouvidoria.ufscar.br) e CPE-UFSCar / Fala.BR.</t>
         </is>
@@ -4175,15 +4546,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
           <t>https://www.fapunifesp.edu.br</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>Canal de comunicação direta para transparência/compliance; LGPD e Portal da Transparência.</t>
         </is>
@@ -4227,15 +4603,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
           <t>https://fapto.org.br</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Menciona canal de denúncias confidencial + Portal de Transparência (com falhas apontadas pela CGU). Ouvidoria nominal a confirmar.</t>
         </is>
